--- a/courses/Micro-And-Macro-Economics/projects/accounting-profit-economic-profit-economic-rent/rideshare-driver-economics-key.xlsx
+++ b/courses/Micro-And-Macro-Economics/projects/accounting-profit-economic-profit-economic-rent/rideshare-driver-economics-key.xlsx
@@ -334,7 +334,7 @@
     <numFmt numFmtId="166" formatCode="0.0%"/>
     <numFmt numFmtId="167" formatCode="\$#,##0;&quot;($&quot;#,##0\);\-"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="18">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -392,8 +392,76 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FF595959"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF0070C0"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFC00000"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF4F6228"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -418,6 +486,42 @@
         <bgColor rgb="FFCCFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B5E40"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDE9D9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border diagonalUp="false" diagonalDown="false">
@@ -453,7 +557,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="43">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -528,6 +632,102 @@
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf applyFill="1" numFmtId="164" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf applyFill="1" numFmtId="164" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf applyFill="1" numFmtId="165" fontId="11" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf applyFill="1" numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf applyFill="1" numFmtId="166" fontId="11" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf applyFill="1" numFmtId="167" fontId="11" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf applyFill="1" numFmtId="165" fontId="11" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf applyFill="1" numFmtId="164" fontId="13" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf applyFill="1" numFmtId="165" fontId="14" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf applyFill="1" numFmtId="167" fontId="14" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf applyFill="1" numFmtId="166" fontId="11" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf applyFill="1" numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf applyFill="1" numFmtId="164" fontId="11" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf applyFill="1" numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf applyFill="1" numFmtId="164" fontId="13" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf applyFill="1" numFmtId="164" fontId="11" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf applyFill="1" numFmtId="164" fontId="14" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf applyFill="1" numFmtId="164" fontId="16" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf applyFill="1" numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf applyFill="1" numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf applyFill="1" numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf applyFill="1" numFmtId="164" fontId="11" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf applyFill="1" numFmtId="164" fontId="11" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf applyFill="1" numFmtId="164" fontId="11" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -782,7 +982,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:B19"/>
+  <dimension ref="B2:B26"/>
   <sheetFormatPr defaultColWidth="8.453125" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="112"/>
@@ -812,8 +1012,10 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="3" t="s">
-        <v>4</v>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Cell colours follow the house legend at the bottom of this sheet: tan = hardcoded input, blue-on-grey = formula (do not overtype), yellow = a fitted/judgmental key assumption.</t>
+        </is>
       </c>
     </row>
     <row r="9" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -844,24 +1046,81 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="6" t="s">
-        <v>13</v>
+    <row r="16" spans="2:2">
+      <c r="B16" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">COLOR CODING LEGEND  —  the house convention (see WORKBOOK-STANDARDS.md)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" spans="2:2">
+      <c r="B17" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Input — hardcoded:  black text on tan.  A number typed in, not calculated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" spans="2:2">
+      <c r="B18" s="35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Formula — calculated:  blue text on light grey.  Derived from cells on this sheet. Never type over it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" spans="2:2">
+      <c r="B19" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Link — another sheet:  olive text on light grey.  Pulls a value from another sheet in this workbook.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" spans="2:2">
+      <c r="B20" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">External source:  red text.  A live reference to another file. Avoided here — external figures are typed in as tan hardcodes with a source note.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" spans="2:2">
+      <c r="B21" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Warning / caveat:  bold dark red.  Something the model cannot do, or a basis inconsistency to state out loud.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" spans="2:2">
+      <c r="B22" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Source note:  grey italic, 9pt.  Provenance, vintage, or method commentary — not part of the calculation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" spans="2:2">
+      <c r="B23" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Header:  white bold on dark green.  Column or table header row.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" spans="2:2">
+      <c r="B24" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Key assumption:  black text on yellow.  A FITTED or judgmental input rather than an observed one — the first thing to challenge.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" spans="2:2">
+      <c r="B25" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Solver objective:  gold fill.  The cell Solver optimizes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" spans="2:2">
+      <c r="B26" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Solver constraint:  light red fill.  Cells Solver is constrained to (caps and limits named in the Solver model).</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -896,20 +1155,20 @@
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="20"/>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="9" t="n">
+      <c r="C5" s="21" t="n">
         <v>30</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="22" t="s">
         <v>17</v>
       </c>
     </row>
@@ -917,10 +1176,10 @@
       <c r="B6" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="10" t="n">
+      <c r="C6" s="23" t="n">
         <v>0.25</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="22" t="s">
         <v>19</v>
       </c>
     </row>
@@ -928,7 +1187,7 @@
       <c r="B7" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="11" t="n">
+      <c r="C7" s="24" t="n">
         <v>20</v>
       </c>
     </row>
@@ -936,7 +1195,7 @@
       <c r="B8" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C8" s="9" t="n">
+      <c r="C8" s="25" t="n">
         <v>8</v>
       </c>
     </row>
@@ -944,28 +1203,28 @@
       <c r="B9" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="11" t="n">
+      <c r="C9" s="24" t="n">
         <v>450</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="22" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="12"/>
-      <c r="C11" s="12" t="s">
+      <c r="B11" s="26"/>
+      <c r="C11" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="D11" s="12" t="s">
+      <c r="D11" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="E11" s="12" t="s">
+      <c r="E11" s="26" t="s">
         <v>26</v>
       </c>
-      <c r="F11" s="12" t="s">
+      <c r="F11" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="G11" s="12" t="s">
+      <c r="G11" s="26" t="s">
         <v>28</v>
       </c>
     </row>
@@ -973,13 +1232,13 @@
       <c r="B12" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C12" s="9" t="n">
+      <c r="C12" s="25" t="n">
         <v>20</v>
       </c>
-      <c r="D12" s="9" t="n">
+      <c r="D12" s="25" t="n">
         <v>10</v>
       </c>
-      <c r="E12" s="9" t="n">
+      <c r="E12" s="25" t="n">
         <v>30</v>
       </c>
     </row>
@@ -987,13 +1246,13 @@
       <c r="B13" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C13" s="11" t="n">
+      <c r="C13" s="24" t="n">
         <v>12</v>
       </c>
-      <c r="D13" s="11" t="n">
+      <c r="D13" s="24" t="n">
         <v>12</v>
       </c>
-      <c r="E13" s="11" t="n">
+      <c r="E13" s="24" t="n">
         <v>10</v>
       </c>
     </row>
@@ -1001,20 +1260,20 @@
       <c r="B14" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C14" s="9" t="n">
+      <c r="C14" s="25" t="n">
         <v>8</v>
       </c>
-      <c r="D14" s="9" t="n">
+      <c r="D14" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="E14" s="9" t="n">
+      <c r="E14" s="25" t="n">
         <v>10</v>
       </c>
-      <c r="F14" s="13" t="n">
+      <c r="F14" s="27" t="n">
         <f aca="false">rs_hours</f>
         <v>8</v>
       </c>
-      <c r="G14" s="5" t="s">
+      <c r="G14" s="22" t="s">
         <v>32</v>
       </c>
     </row>
@@ -1022,19 +1281,19 @@
       <c r="B15" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C15" s="14" t="n">
+      <c r="C15" s="28" t="n">
         <f aca="false">C12*C13*rs_days</f>
         <v>7200</v>
       </c>
-      <c r="D15" s="14" t="n">
+      <c r="D15" s="28" t="n">
         <f aca="false">D12*D13*rs_days</f>
         <v>3600</v>
       </c>
-      <c r="E15" s="14" t="n">
+      <c r="E15" s="28" t="n">
         <f aca="false">E12*E13*rs_days</f>
         <v>9000</v>
       </c>
-      <c r="F15" s="14" t="n">
+      <c r="F15" s="28" t="n">
         <f aca="false">rs_wage*rs_hours*rs_days</f>
         <v>4800</v>
       </c>
@@ -1048,13 +1307,13 @@
       <c r="B17" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="C17" s="11" t="n">
+      <c r="C17" s="24" t="n">
         <v>250</v>
       </c>
-      <c r="D17" s="11" t="n">
+      <c r="D17" s="24" t="n">
         <v>250</v>
       </c>
-      <c r="G17" s="5" t="s">
+      <c r="G17" s="22" t="s">
         <v>36</v>
       </c>
     </row>
@@ -1062,10 +1321,10 @@
       <c r="B18" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C18" s="11" t="n">
+      <c r="C18" s="24" t="n">
         <v>150</v>
       </c>
-      <c r="D18" s="11" t="n">
+      <c r="D18" s="24" t="n">
         <v>150</v>
       </c>
     </row>
@@ -1073,16 +1332,16 @@
       <c r="B19" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="C19" s="11" t="n">
+      <c r="C19" s="24" t="n">
         <v>690</v>
       </c>
-      <c r="D19" s="11" t="n">
+      <c r="D19" s="24" t="n">
         <v>345</v>
       </c>
-      <c r="E19" s="11" t="n">
+      <c r="E19" s="24" t="n">
         <v>1035</v>
       </c>
-      <c r="G19" s="5" t="s">
+      <c r="G19" s="22" t="s">
         <v>39</v>
       </c>
     </row>
@@ -1090,10 +1349,10 @@
       <c r="B20" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C20" s="11" t="n">
+      <c r="C20" s="24" t="n">
         <v>100</v>
       </c>
-      <c r="D20" s="11" t="n">
+      <c r="D20" s="24" t="n">
         <v>50</v>
       </c>
     </row>
@@ -1101,15 +1360,15 @@
       <c r="B21" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C21" s="15" t="n">
+      <c r="C21" s="28" t="n">
         <f aca="false">C15*rs_comm</f>
         <v>1800</v>
       </c>
-      <c r="D21" s="15" t="n">
+      <c r="D21" s="28" t="n">
         <f aca="false">D15*rs_comm</f>
         <v>900</v>
       </c>
-      <c r="G21" s="5" t="s">
+      <c r="G21" s="22" t="s">
         <v>41</v>
       </c>
     </row>
@@ -1117,10 +1376,10 @@
       <c r="B22" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="E22" s="11" t="n">
+      <c r="E22" s="24" t="n">
         <v>3000</v>
       </c>
-      <c r="G22" s="5" t="s">
+      <c r="G22" s="22" t="s">
         <v>43</v>
       </c>
     </row>
@@ -1128,7 +1387,7 @@
       <c r="B23" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="F23" s="15" t="n">
+      <c r="F23" s="28" t="n">
         <f aca="false">rs_commute</f>
         <v>450</v>
       </c>
@@ -1137,19 +1396,19 @@
       <c r="B24" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C24" s="14" t="n">
+      <c r="C24" s="28" t="n">
         <f aca="false">SUM(C17:C21)</f>
         <v>2990</v>
       </c>
-      <c r="D24" s="14" t="n">
+      <c r="D24" s="28" t="n">
         <f aca="false">SUM(D17:D21)</f>
         <v>1695</v>
       </c>
-      <c r="E24" s="14" t="n">
+      <c r="E24" s="28" t="n">
         <f aca="false">SUM(E19:E22)</f>
         <v>4035</v>
       </c>
-      <c r="F24" s="14" t="n">
+      <c r="F24" s="28" t="n">
         <f aca="false">F23</f>
         <v>450</v>
       </c>
@@ -1158,19 +1417,19 @@
       <c r="B26" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C26" s="14" t="n">
+      <c r="C26" s="28" t="n">
         <f aca="false">C15*12</f>
         <v>86400</v>
       </c>
-      <c r="D26" s="14" t="n">
+      <c r="D26" s="28" t="n">
         <f aca="false">D15*12</f>
         <v>43200</v>
       </c>
-      <c r="E26" s="14" t="n">
+      <c r="E26" s="28" t="n">
         <f aca="false">E15*12</f>
         <v>108000</v>
       </c>
-      <c r="F26" s="14" t="n">
+      <c r="F26" s="28" t="n">
         <f aca="false">F15*12</f>
         <v>57600</v>
       </c>
@@ -1179,19 +1438,19 @@
       <c r="B27" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="C27" s="15" t="n">
+      <c r="C27" s="28" t="n">
         <f aca="false">C24*12</f>
         <v>35880</v>
       </c>
-      <c r="D27" s="15" t="n">
+      <c r="D27" s="28" t="n">
         <f aca="false">D24*12</f>
         <v>20340</v>
       </c>
-      <c r="E27" s="15" t="n">
+      <c r="E27" s="28" t="n">
         <f aca="false">E24*12</f>
         <v>48420</v>
       </c>
-      <c r="F27" s="15" t="n">
+      <c r="F27" s="28" t="n">
         <f aca="false">F24*12</f>
         <v>5400</v>
       </c>
@@ -1200,23 +1459,23 @@
       <c r="B28" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C28" s="16" t="n">
+      <c r="C28" s="28" t="n">
         <f aca="false">C26-C27</f>
         <v>50520</v>
       </c>
-      <c r="D28" s="16" t="n">
+      <c r="D28" s="28" t="n">
         <f aca="false">D26-D27</f>
         <v>22860</v>
       </c>
-      <c r="E28" s="16" t="n">
+      <c r="E28" s="28" t="n">
         <f aca="false">E26-E27</f>
         <v>59580</v>
       </c>
-      <c r="F28" s="16" t="n">
+      <c r="F28" s="28" t="n">
         <f aca="false">F26-F27</f>
         <v>52200</v>
       </c>
-      <c r="G28" s="5" t="s">
+      <c r="G28" s="22" t="s">
         <v>49</v>
       </c>
     </row>
@@ -1224,23 +1483,23 @@
       <c r="B29" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="C29" s="17" t="n">
+      <c r="C29" s="28" t="n">
         <f aca="false">rs_acct_trad</f>
         <v>52200</v>
       </c>
-      <c r="D29" s="17" t="n">
+      <c r="D29" s="28" t="n">
         <f aca="false">rs_acct_trad/2</f>
         <v>26100</v>
       </c>
-      <c r="E29" s="17" t="n">
+      <c r="E29" s="28" t="n">
         <f aca="false">rs_acct_trad</f>
         <v>52200</v>
       </c>
-      <c r="F29" s="17" t="n">
+      <c r="F29" s="28" t="n">
         <f aca="false">rs_acct_uberft</f>
         <v>50520</v>
       </c>
-      <c r="G29" s="5" t="s">
+      <c r="G29" s="22" t="s">
         <v>51</v>
       </c>
     </row>
@@ -1248,23 +1507,23 @@
       <c r="B30" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C30" s="16" t="n">
+      <c r="C30" s="28" t="n">
         <f aca="false">C28-C29</f>
         <v>-1680</v>
       </c>
-      <c r="D30" s="16" t="n">
+      <c r="D30" s="28" t="n">
         <f aca="false">D28-D29</f>
         <v>-3240</v>
       </c>
-      <c r="E30" s="16" t="n">
+      <c r="E30" s="28" t="n">
         <f aca="false">E28-E29</f>
         <v>7380</v>
       </c>
-      <c r="F30" s="16" t="n">
+      <c r="F30" s="28" t="n">
         <f aca="false">F28-F29</f>
         <v>1680</v>
       </c>
-      <c r="G30" s="5" t="s">
+      <c r="G30" s="22" t="s">
         <v>53</v>
       </c>
     </row>
@@ -1272,34 +1531,34 @@
       <c r="B31" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="C31" s="17" t="n">
+      <c r="C31" s="28" t="n">
         <f aca="false">C29</f>
         <v>52200</v>
       </c>
-      <c r="D31" s="17" t="n">
+      <c r="D31" s="28" t="n">
         <f aca="false">D29</f>
         <v>26100</v>
       </c>
-      <c r="E31" s="17" t="n">
+      <c r="E31" s="28" t="n">
         <f aca="false">E29</f>
         <v>52200</v>
       </c>
-      <c r="F31" s="17" t="n">
+      <c r="F31" s="28" t="n">
         <f aca="false">F29</f>
         <v>50520</v>
       </c>
-      <c r="G31" s="5" t="s">
+      <c r="G31" s="22" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="7" t="s">
+      <c r="B33" s="19" t="s">
         <v>56</v>
       </c>
-      <c r="C33" s="8"/>
-      <c r="D33" s="8"/>
-      <c r="E33" s="8"/>
-      <c r="F33" s="8"/>
+      <c r="C33" s="20"/>
+      <c r="D33" s="20"/>
+      <c r="E33" s="20"/>
+      <c r="F33" s="20"/>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="5" t="s">
@@ -1358,22 +1617,22 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="19" t="s">
         <v>63</v>
       </c>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
+      <c r="C5" s="20"/>
+      <c r="D5" s="20"/>
+      <c r="E5" s="20"/>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="12"/>
-      <c r="C6" s="12" t="s">
+      <c r="B6" s="26"/>
+      <c r="C6" s="26" t="s">
         <v>64</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="26" t="s">
         <v>65</v>
       </c>
-      <c r="E6" s="12" t="s">
+      <c r="E6" s="26" t="s">
         <v>28</v>
       </c>
     </row>
@@ -1381,13 +1640,13 @@
       <c r="B7" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="C7" s="11" t="n">
+      <c r="C7" s="24" t="n">
         <v>3000</v>
       </c>
-      <c r="D7" s="11" t="n">
+      <c r="D7" s="24" t="n">
         <v>1500</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="22" t="s">
         <v>67</v>
       </c>
     </row>
@@ -1395,11 +1654,11 @@
       <c r="B8" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="C8" s="15" t="n">
+      <c r="C8" s="28" t="n">
         <f aca="false">C7*12</f>
         <v>36000</v>
       </c>
-      <c r="D8" s="15" t="n">
+      <c r="D8" s="28" t="n">
         <f aca="false">D7*12</f>
         <v>18000</v>
       </c>
@@ -1408,13 +1667,13 @@
       <c r="B9" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="C9" s="10" t="n">
+      <c r="C9" s="29" t="n">
         <v>0.035</v>
       </c>
-      <c r="D9" s="10" t="n">
+      <c r="D9" s="29" t="n">
         <v>0.06</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E9" s="22" t="s">
         <v>70</v>
       </c>
     </row>
@@ -1422,15 +1681,15 @@
       <c r="B10" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="C10" s="16" t="n">
+      <c r="C10" s="28" t="n">
         <f aca="false">C8/C9</f>
         <v>1028571.42857143</v>
       </c>
-      <c r="D10" s="16" t="n">
+      <c r="D10" s="28" t="n">
         <f aca="false">D8/D9</f>
         <v>300000</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="E10" s="22" t="s">
         <v>72</v>
       </c>
     </row>
@@ -1438,86 +1697,86 @@
       <c r="B11" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="22" t="s">
         <v>74</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D11" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="E11" s="22" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="C13" s="8"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="20"/>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="C14" s="18" t="s">
+      <c r="C14" s="30" t="s">
         <v>79</v>
       </c>
-      <c r="D14" s="18"/>
-      <c r="E14" s="18"/>
+      <c r="D14" s="31"/>
+      <c r="E14" s="31"/>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="C15" s="18" t="s">
+      <c r="C15" s="30" t="s">
         <v>81</v>
       </c>
-      <c r="D15" s="18"/>
-      <c r="E15" s="18"/>
+      <c r="D15" s="31"/>
+      <c r="E15" s="31"/>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="C16" s="18" t="s">
+      <c r="C16" s="30" t="s">
         <v>83</v>
       </c>
-      <c r="D16" s="18"/>
-      <c r="E16" s="18"/>
+      <c r="D16" s="31"/>
+      <c r="E16" s="31"/>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="C17" s="18" t="s">
+      <c r="C17" s="30" t="s">
         <v>85</v>
       </c>
-      <c r="D17" s="18"/>
-      <c r="E17" s="18"/>
+      <c r="D17" s="31"/>
+      <c r="E17" s="31"/>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="C18" s="18" t="s">
+      <c r="C18" s="30" t="s">
         <v>87</v>
       </c>
-      <c r="D18" s="18"/>
-      <c r="E18" s="18"/>
+      <c r="D18" s="31"/>
+      <c r="E18" s="31"/>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="7" t="s">
+      <c r="B20" s="19" t="s">
         <v>88</v>
       </c>
-      <c r="C20" s="8"/>
-      <c r="D20" s="8"/>
+      <c r="C20" s="20"/>
+      <c r="D20" s="20"/>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C21" s="22" t="s">
         <v>90</v>
       </c>
     </row>
@@ -1525,7 +1784,7 @@
       <c r="B22" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="C22" s="5" t="s">
+      <c r="C22" s="22" t="s">
         <v>92</v>
       </c>
     </row>
@@ -1533,7 +1792,7 @@
       <c r="B23" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="C23" s="5" t="s">
+      <c r="C23" s="22" t="s">
         <v>94</v>
       </c>
     </row>
@@ -1541,7 +1800,7 @@
       <c r="B24" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="C24" s="5" t="s">
+      <c r="C24" s="32" t="s">
         <v>96</v>
       </c>
     </row>
